--- a/Month-1/Day-10/Riyadh_Customer_Service_Salary_Analysis.xlsx
+++ b/Month-1/Day-10/Riyadh_Customer_Service_Salary_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data-Analysis-and-AI-85Days\Month-1\Day-10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{051CFDA1-583D-4A7B-8D08-9C7308FA900A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173B08F1-55A9-4C55-89E7-3C0B44C2A8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{32196388-CACF-4670-A430-723426D052A8}"/>
   </bookViews>
@@ -150,7 +150,7 @@
     <numFmt numFmtId="164" formatCode="[$⃁-401]\ #,##0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1673,10 +1673,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ahmed" refreshedDate="46210.674807870368" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{FA42F13D-1E93-4574-B0D2-AA761DEF8408}">
   <cacheSource type="worksheet">
@@ -2425,18 +2421,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E586F6A-1E93-49B4-931D-B0F83CAF701F}">
   <dimension ref="A1:N53"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.6328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.36328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" thickBot="1">
+    <row r="1" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
@@ -2445,7 +2441,7 @@
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
     </row>
-    <row r="2" spans="1:14" ht="16">
+    <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -2456,7 +2452,7 @@
       </c>
       <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -2479,7 +2475,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -2502,7 +2498,7 @@
         <v>9171.4</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>2</v>
       </c>
@@ -2525,7 +2521,7 @@
         <v>993.19579055055749</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -2548,7 +2544,7 @@
         <v>6725</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>4</v>
       </c>
@@ -2571,7 +2567,7 @@
         <v>7022.9547854423317</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -2594,7 +2590,7 @@
         <v>49321893.918367349</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>6</v>
       </c>
@@ -2617,7 +2613,7 @@
         <v>14.750746578978276</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>7</v>
       </c>
@@ -2640,7 +2636,7 @@
         <v>3.5531978281890599</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>8</v>
       </c>
@@ -2663,7 +2659,7 @@
         <v>39900</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>9</v>
       </c>
@@ -2680,7 +2676,7 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>10</v>
       </c>
@@ -2697,7 +2693,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>11</v>
       </c>
@@ -2714,7 +2710,7 @@
         <v>458570</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>12</v>
       </c>
@@ -2731,7 +2727,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>13</v>
       </c>
@@ -2742,7 +2738,7 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>14</v>
       </c>
@@ -2755,7 +2751,7 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>15</v>
       </c>
@@ -2766,7 +2762,7 @@
         <v>5350</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>16</v>
       </c>
@@ -2777,7 +2773,7 @@
         <v>5650</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>17</v>
       </c>
@@ -2788,7 +2784,7 @@
         <v>5850</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>18</v>
       </c>
@@ -2799,7 +2795,7 @@
         <v>5750</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
         <v>19</v>
       </c>
@@ -2810,7 +2806,7 @@
         <v>6050</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>20</v>
       </c>
@@ -2821,7 +2817,7 @@
         <v>5250</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>21</v>
       </c>
@@ -2832,7 +2828,7 @@
         <v>5550</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>22</v>
       </c>
@@ -2843,7 +2839,7 @@
         <v>5620</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>23</v>
       </c>
@@ -2855,7 +2851,7 @@
       </c>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>24</v>
       </c>
@@ -2866,7 +2862,7 @@
         <v>5920</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>25</v>
       </c>
@@ -2877,7 +2873,7 @@
         <v>6150</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>26</v>
       </c>
@@ -2888,7 +2884,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>27</v>
       </c>
@@ -2899,7 +2895,7 @@
         <v>7800</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>28</v>
       </c>
@@ -2910,7 +2906,7 @@
         <v>7200</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>29</v>
       </c>
@@ -2921,7 +2917,7 @@
         <v>8100</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="7">
         <v>30</v>
       </c>
@@ -2932,7 +2928,7 @@
         <v>7900</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="7">
         <v>31</v>
       </c>
@@ -2943,7 +2939,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>32</v>
       </c>
@@ -2954,7 +2950,7 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="7">
         <v>33</v>
       </c>
@@ -2965,7 +2961,7 @@
         <v>7400</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="7">
         <v>34</v>
       </c>
@@ -2976,7 +2972,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <v>35</v>
       </c>
@@ -2987,7 +2983,7 @@
         <v>7700</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <v>36</v>
       </c>
@@ -2998,7 +2994,7 @@
         <v>8200</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>37</v>
       </c>
@@ -3009,7 +3005,7 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="7">
         <v>38</v>
       </c>
@@ -3020,7 +3016,7 @@
         <v>7950</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="7">
         <v>39</v>
       </c>
@@ -3031,7 +3027,7 @@
         <v>11500</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
         <v>40</v>
       </c>
@@ -3042,7 +3038,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>41</v>
       </c>
@@ -3053,7 +3049,7 @@
         <v>11800</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>42</v>
       </c>
@@ -3064,7 +3060,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>43</v>
       </c>
@@ -3075,7 +3071,7 @@
         <v>11200</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="7">
         <v>44</v>
       </c>
@@ -3086,7 +3082,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>45</v>
       </c>
@@ -3097,7 +3093,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="7">
         <v>46</v>
       </c>
@@ -3108,7 +3104,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>47</v>
       </c>
@@ -3119,7 +3115,7 @@
         <v>15500</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="7">
         <v>48</v>
       </c>
@@ -3130,7 +3126,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>49</v>
       </c>
@@ -3141,7 +3137,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="7">
         <v>50</v>
       </c>
@@ -3206,23 +3202,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C75CCA8C93D93A43A1AC488E2F0D8821" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5345ce98933d9ec1471464f61cd0e19e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="22654faffaec1724d19dfafa100f8372" ns3:_="">
     <xsd:import namespace="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf"/>
@@ -3372,31 +3351,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B36ED1D6-A2C8-4A92-B59E-1A90CD0726A5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FAA6EE3-6AEA-4AC3-BDFE-DD8C2CD0A3A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C28B917-97FF-4E7F-8946-3A0FA4458800}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3412,4 +3384,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FAA6EE3-6AEA-4AC3-BDFE-DD8C2CD0A3A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B36ED1D6-A2C8-4A92-B59E-1A90CD0726A5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>